--- a/EXCEL/Data/arbejdstid_data/arbejdstid_klassificering.xlsx
+++ b/EXCEL/Data/arbejdstid_data/arbejdstid_klassificering.xlsx
@@ -94,7 +94,7 @@
     <t>Datasæt 02 2021</t>
   </si>
   <si>
-    <t>Kørsel 8.4.2026 13.58.36</t>
+    <t>Kørsel 14.4.2026 12.27.43</t>
   </si>
   <si>
     <t>BEMÆRK Rapport-typen er ændret en smule pr. 4/3-/020: se &lt;a href="https://krl.dk/#/forum?post=638"&gt;KRL-forum:  638&lt;/a&gt;</t>
